--- a/images/electrical/Chel_Electrical_Master_Netlist.xlsx
+++ b/images/electrical/Chel_Electrical_Master_Netlist.xlsx
@@ -405,7 +405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K139"/>
+  <dimension ref="A1:K143"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="22" customWidth="1" style="3" min="1" max="1"/>
@@ -4796,12 +4796,12 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>AUX LT switch feed</t>
+          <t>TAN-park light feed (front harness)</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Tan</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
@@ -4811,17 +4811,17 @@
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>Headlight switch AUX LT position</t>
+          <t>TAN-park light circuit (existing)</t>
         </is>
       </c>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>Interlock relay (repurposed FFR fuel-pump relay socket, see row 15/flag 10)</t>
+          <t>NUM LT lamps, door L/R + tail (parallel tap)</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H81" s="6" t="inlineStr">
@@ -4836,12 +4836,12 @@
       </c>
       <c r="J81" s="6" t="inlineStr">
         <is>
-          <t>Hardware position decided — relay socket freed up</t>
+          <t>SIMPLIFIED — relay removed per Aaron</t>
         </is>
       </c>
       <c r="K81" s="6" t="inlineStr">
         <is>
-          <t>Since Holley's fuel pump now runs off its own dedicated relay/fuse at the battery (flag 10), the FFR chassis fuse-block's original fuel-pump relay socket is unused — reusing that physical relay position and fuse slot for this interlock relay instead of adding new hardware to the board.</t>
+          <t>Aaron: no relay needed — combined draw for AUX (door L/R) + front park + tail is under 3A with incandescent bulbs, well within the park circuit's existing headroom. NUM LT lamps now wire in parallel directly off the same Tan park-feed wire, no separate switch or relay. This also naturally preserves 'only on when park lights on' behavior without added hardware. Simplified during Full Wiring Master Sheet build.</t>
         </is>
       </c>
     </row>
@@ -4851,36 +4851,16 @@
           <t>Aux/Racing Number Lights</t>
         </is>
       </c>
-      <c r="B82" s="6" t="inlineStr">
-        <is>
-          <t>Park light feed (interlock enable)</t>
-        </is>
-      </c>
-      <c r="C82" s="6" t="inlineStr">
-        <is>
-          <t>Tan</t>
-        </is>
-      </c>
+      <c r="B82" s="6" t="inlineStr"/>
+      <c r="C82" s="6" t="inlineStr"/>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>Interlock enable for racing number lights</t>
-        </is>
-      </c>
-      <c r="E82" s="6" t="inlineStr">
-        <is>
-          <t>TAN-park light circuits (front harness)</t>
-        </is>
-      </c>
-      <c r="F82" s="6" t="inlineStr">
-        <is>
-          <t>Relay coil enable leg</t>
-        </is>
-      </c>
-      <c r="G82" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>SUPERSEDED — see row 81</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="inlineStr"/>
+      <c r="F82" s="6" t="inlineStr"/>
+      <c r="G82" s="6" t="inlineStr"/>
       <c r="H82" s="6" t="inlineStr">
         <is>
           <t>FFR Chassis Harness Rev W (diagram Rev T)</t>
@@ -4893,12 +4873,12 @@
       </c>
       <c r="J82" s="6" t="inlineStr">
         <is>
-          <t>Design finalized — single relay, no diode needed</t>
+          <t>REMOVED — relay no longer used</t>
         </is>
       </c>
       <c r="K82" s="6" t="inlineStr">
         <is>
-          <t>AND-gate achieved with one 5-pin relay: coil (85/86) wired to Park Light circuit (ground + switched feed) so the relay only closes when parking lights are on; common (30) fed FROM the Aux LT switch output rather than direct battery, so power only reaches the output (87) if the Aux switch is also on. Both conditions required — true interlock, no diodes required.</t>
+          <t>This AND-gate relay design (park light coil + Aux switch common) is no longer needed — see row 81. The FFR fuel-pump relay socket this was going to repurpose is now open again for other future use.</t>
         </is>
       </c>
     </row>
@@ -4910,12 +4890,12 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>Racing number lamp power (door L/R + tail)</t>
+          <t>Brown, off park feed (parallel tap)</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Brown/Tan</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
@@ -4925,17 +4905,17 @@
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>Interlock relay output</t>
+          <t>TAN-park light feed</t>
         </is>
       </c>
       <c r="F83" s="6" t="inlineStr">
         <is>
-          <t>Interlock relay output (repurposed FFR fuel-pump relay socket)</t>
+          <t>NUM LT lamps (door harness L/R + tail)</t>
         </is>
       </c>
       <c r="G83" s="6" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>shares park circuit fuse</t>
         </is>
       </c>
       <c r="H83" s="6" t="inlineStr">
@@ -4950,12 +4930,12 @@
       </c>
       <c r="J83" s="6" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>SIMPLIFIED — no dedicated fuse/relay needed</t>
         </is>
       </c>
       <c r="K83" s="6" t="inlineStr">
         <is>
-          <t>Similar lamp style to license plate light per Aaron; run as its own small sub-harness. Fuse amperage TBD once actual lamp wattage is known (pull from parts list when lamps are purchased) — reuses the freed fuse-block position's fuse slot, just needs correct amp rating swapped in.</t>
+          <t>Runs through the new Door Harness (L) and (R) sub-harnesses (rows 140-141) and continues to the tail per the Full Wiring Master Sheet. Lamp style similar to license plate light per Aaron. No dedicated fuse — rides the existing park-feed circuit given the low combined current draw.</t>
         </is>
       </c>
     </row>
@@ -8001,12 +7981,12 @@
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>DK BLUE-REVERSE LT</t>
+          <t>ORANGE-REVERSE LT</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>Dk Blue</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
@@ -8041,69 +8021,297 @@
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
-          <t>NEW — color chosen for zero conflict risk</t>
+          <t>COLOR CORRECTED — Orange, not Dk Blue</t>
         </is>
       </c>
       <c r="K138" s="3" t="inlineStr">
         <is>
-          <t>Dk Blue isn't used elsewhere in the front/rear lighting harness, so it won't be confused with an existing circuit when bundled physically with the brake light wiring per Aaron's request. Grounds via chassis ground bus — needs a dedicated ground wire per the fiberglass-body finding (see Ground Scheme sheet / Open Flag 22), not a body-contact ground.</t>
+          <t>Superseded the earlier Dark Blue pick (chosen only for zero-conflict, arbitrarily) — Aaron's own traced reference art consistently shows Orange for both the TKX reverse sensor lead and the reverse lamp feed, so adopting that instead. Orange isn't used elsewhere in the rear lighting harness, so no conflict risk either way. Corrected during Full Wiring Master Sheet build.</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr">
+      <c r="A139" s="3" t="inlineStr">
         <is>
           <t>Interior/Courtesy Light (not yet on Lighting sheet)</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr">
+      <c r="B139" s="3" t="inlineStr">
         <is>
           <t>Door jamb switch(es) → interior lamp</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr">
+      <c r="C139" s="3" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr">
+      <c r="D139" s="3" t="inlineStr">
         <is>
           <t>Momentary door switch, normally-closed logic: door open = switch not pressed = light ON; door closed = switch pressed = light OFF</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr">
+      <c r="E139" s="3" t="inlineStr">
         <is>
           <t>Door jamb switch(es), one or two doors — TBD</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr">
+      <c r="F139" s="3" t="inlineStr">
         <is>
           <t>Interior/courtesy lamp</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr">
+      <c r="G139" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H139" s="3" t="inlineStr">
         <is>
           <t>n/a — not yet detailed, only the fuse is reserved</t>
         </is>
       </c>
-      <c r="I139" t="inlineStr">
+      <c r="I139" s="3" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="J139" t="inlineStr">
+      <c r="J139" s="3" t="inlineStr">
         <is>
           <t>FUTURE — capture only, not built yet</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr">
+      <c r="K139" s="3" t="inlineStr">
         <is>
           <t>Aaron wants a momentary-switch interior light: open door = light on, door closed and button physically pressed = light off. This is standard door-jamb-switch courtesy light behavior. The fuse already exists and is reserved on the Power &amp; Fuse Block sheet (HDLT SW/RADIO MEM/COURTESY LT, BAT FED bus, 15A, always-hot) — it's just never been wired out to an actual switch/lamp. Work into Lighting sheet on a future update.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="3" t="inlineStr">
+        <is>
+          <t>Fog Lights (new dedicated circuit)</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>New 15A fuse, AUX FUSE PANEL</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D140" s="3" t="inlineStr">
+        <is>
+          <t>Dedicated power for L/R fog lights, separate from headlight circuit</t>
+        </is>
+      </c>
+      <c r="E140" s="3" t="inlineStr">
+        <is>
+          <t>FL S. switch (dash, already planned by Aaron)</t>
+        </is>
+      </c>
+      <c r="F140" s="3" t="inlineStr">
+        <is>
+          <t>AUX FUSE PANEL (new, position TBD)</t>
+        </is>
+      </c>
+      <c r="G140" s="3" t="inlineStr">
+        <is>
+          <t>15A</t>
+        </is>
+      </c>
+      <c r="H140" s="3" t="inlineStr">
+        <is>
+          <t>n/a — new circuit, not in FFR harness</t>
+        </is>
+      </c>
+      <c r="I140" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J140" s="3" t="inlineStr">
+        <is>
+          <t>NEW — required by load math, see Open Flag 25</t>
+        </is>
+      </c>
+      <c r="K140" s="3" t="inlineStr">
+        <is>
+          <t>55W headlights (x2) draw ~9.17A; 55W fogs (x2) also draw ~9.17A. Combined on the stock single 15A 'HDLT SW' circuit = ~18.3A, exceeding the fuse. Headlights stay on the existing stock 15A circuit (9.17A + park/tail/AUX ~3A + dash lights ≈ 12-13A, safe margin). Fogs get their own new 15A circuit fed through a new switch (FL S., matches Aaron's own dash plan) and a new AUX FUSE PANEL, since all 11 positions on the primary FFR block are already assigned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="inlineStr">
+        <is>
+          <t>Fog Lights (new dedicated circuit)</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>Red + Black, 2-wire per lamp</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="inlineStr">
+        <is>
+          <t>Red/Black</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="inlineStr">
+        <is>
+          <t>Fog lamp power + ground</t>
+        </is>
+      </c>
+      <c r="E141" s="3" t="inlineStr">
+        <is>
+          <t>AUX FUSE PANEL</t>
+        </is>
+      </c>
+      <c r="F141" s="3" t="inlineStr">
+        <is>
+          <t>L. FL / R. FL</t>
+        </is>
+      </c>
+      <c r="G141" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H141" s="3" t="inlineStr">
+        <is>
+          <t>n/a — new circuit, not in FFR harness</t>
+        </is>
+      </c>
+      <c r="I141" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J141" s="3" t="inlineStr">
+        <is>
+          <t>NEW — matches Aaron's own traced wire colors</t>
+        </is>
+      </c>
+      <c r="K141" s="3" t="inlineStr">
+        <is>
+          <t>Simple 2-wire lamp circuit (unlike headlights, which share a 3-function housing) — matches Aaron's reference art exactly. Needs its own dedicated ground wire per the fiberglass-body finding (Ground Scheme sheet / Open Flag 22).</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="3" t="inlineStr">
+        <is>
+          <t>Door Harness (L) — new sub-harness</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>Breaks off main harness under dash</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D142" s="3" t="inlineStr">
+        <is>
+          <t>Bundles door popper + AUX (NUM LT) + courtesy switch for the left door</t>
+        </is>
+      </c>
+      <c r="E142" s="3" t="inlineStr">
+        <is>
+          <t>Main harness, under-dash breakout</t>
+        </is>
+      </c>
+      <c r="F142" s="3" t="inlineStr">
+        <is>
+          <t>Door popper, NUM LT (park feed tap), CLT S.</t>
+        </is>
+      </c>
+      <c r="G142" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H142" s="3" t="inlineStr">
+        <is>
+          <t>n/a — new sub-harness, not in FFR harness</t>
+        </is>
+      </c>
+      <c r="I142" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J142" s="3" t="inlineStr">
+        <is>
+          <t>NEW — per Aaron, traces alongside main harness</t>
+        </is>
+      </c>
+      <c r="K142" s="3" t="inlineStr">
+        <is>
+          <t>Aaron is building this as its own traceable sub-harness rather than routing each door circuit individually. Door popper fuse/relay sizing still TBD (see Open Flag 26). Courtesy switch (CLT S.) color/logic still open (Open Flag 23).</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="3" t="inlineStr">
+        <is>
+          <t>Door Harness (R) — new sub-harness</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>Breaks off main harness under dash</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="inlineStr">
+        <is>
+          <t>Bundles door popper + AUX (NUM LT) + courtesy switch for the right door</t>
+        </is>
+      </c>
+      <c r="E143" s="3" t="inlineStr">
+        <is>
+          <t>Main harness, under-dash breakout</t>
+        </is>
+      </c>
+      <c r="F143" s="3" t="inlineStr">
+        <is>
+          <t>Door popper, NUM LT (park feed tap), CLT S.</t>
+        </is>
+      </c>
+      <c r="G143" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H143" s="3" t="inlineStr">
+        <is>
+          <t>n/a — new sub-harness, not in FFR harness</t>
+        </is>
+      </c>
+      <c r="I143" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J143" s="3" t="inlineStr">
+        <is>
+          <t>NEW — symmetric to Door Harness (L)</t>
+        </is>
+      </c>
+      <c r="K143" s="3" t="inlineStr">
+        <is>
+          <t>Mirror of row 142. Same open items apply (popper sizing, courtesy switch spec).</t>
         </is>
       </c>
     </row>
@@ -8121,7 +8329,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4" customWidth="1" style="3" min="1" max="1"/>
@@ -8708,27 +8916,77 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
+      <c r="A24" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>Interior/courtesy light circuit — not yet built</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>Master Netlist row 139; Power &amp; Fuse Block sheet COURTESY LT fuse (row 2)</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>Aaron wants a momentary door-jamb switch triggered interior light (door open = on, door closed/button pressed = off). Fuse position already reserved on Power &amp; Fuse Block sheet but never wired out — needs door switch selection (single vs. per-door), wire color, and lamp placement before it can be added to the Lighting sheet.</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>Open — deferred to a future update per Aaron. Add door switch(es) + lamp to Lighting sheet when ready.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>25</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>AUX FUSE PANEL location — custom panel vs. secondary panel vs. spare capacity</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Master Netlist rows 140-141 (fog light circuit)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Fog lights need a new dedicated 15A circuit — all 11 positions on the primary FFR fuse block are already assigned, so this can't just be a new position on the existing block. Three options: (1) replace with a custom fuse panel, (2) add a small secondary/auxiliary panel for new circuits (fog, and could also house the reverse light fuse), (3) verify the physical panel Aaron actually has (kit docs are generic across multiple FFR models) might have spare capacity beyond the documented 11.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Open — Aaron plans to dig out the physical fuse panel/harness to check for spare capacity before deciding. Diagram shows a placeholder AUX FUSE PANEL pending that decision.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>26</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Door popper fuse/relay sizing</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Master Netlist rows 142-143 (door harnesses L/R)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Door harnesses (L/R) are newly added, bundling the popper solenoid with the AUX light and courtesy switch. Popper solenoids are momentary, higher inrush current than the lighting circuits they're bundled with — needs its own fuse sizing and possibly a relay depending on actual popper current draw, not yet specified.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Open — pending popper hardware selection and current draw spec.</t>
         </is>
       </c>
     </row>
